--- a/output/quickfixclose12_portfolio_daily.xlsx
+++ b/output/quickfixclose12_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>180,735.45</t>
+          <t>178,767.09</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+80.74%</t>
+          <t>+78.77%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>186,907  (+86.91%)</t>
+          <t>185,091  (+85.09%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,838  (6.2 pts of return)</t>
+          <t>4,049  (6.3 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.8x</t>
+          <t>3.7x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.4%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.9 bars</t>
+          <t>4.8 bars</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,297  (-1.27%)</t>
+          <t>-1,310  (-1.27%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5743,22 +5743,70 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>180735.45</v>
+        <v>180902.02</v>
       </c>
       <c r="C186" s="5" t="n">
+        <v>6912.31</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>173989.71</v>
+      </c>
+      <c r="E186" t="n">
+        <v>4</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>180902.02</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>6912.31</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>173989.71</v>
+      </c>
+      <c r="E187" t="n">
+        <v>4</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>178767.09</v>
+      </c>
+      <c r="C188" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D186" s="5" t="n">
-        <v>180735.45</v>
-      </c>
-      <c r="E186" t="n">
+      <c r="D188" s="5" t="n">
+        <v>178767.09</v>
+      </c>
+      <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-2,039); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9904,7 @@
         <v>-35.32</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>208324.53</v>
+        <v>205204.12</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9880,14 +9928,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.04</v>
+        <v>-1.16</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>200437.26</v>
@@ -9896,14 +9952,14 @@
         <v>2786.08</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>-111.44</v>
+        <v>-3231.85</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>208359.85</v>
+        <v>205239.44</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>stop</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose12_portfolio_daily.xlsx
+++ b/output/quickfixclose12_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>178,767.09</t>
+          <t>178,757.72</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+78.77%</t>
+          <t>+78.76%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4,049  (6.3 pts of return)</t>
+          <t>4,059  (6.3 pts of return)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5791,22 +5791,82 @@
         <v>46238</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>178767.09</v>
+        <v>178863.35</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>-0</v>
+        <v>5154.84</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>178767.09</v>
+        <v>173708.51</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-2,039); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+          <t>NY_Natural_Gas_Futures stop (-2,039)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>178863.35</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>10314.16</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>168549.2</v>
+      </c>
+      <c r="E189" t="n">
+        <v>6</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 1,737); Nasdaq_100_E_mini short (risk 1,720); S_P_500_E_mini short (risk 1,703)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>178757.72</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>178757.72</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 1,685)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9818,7 +9878,7 @@
         <v>-50.59</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>208537.39</v>
+        <v>205305.54</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9861,7 +9921,7 @@
         <v>-66.09999999999999</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>208471.29</v>
+        <v>205239.44</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9904,7 +9964,7 @@
         <v>-35.32</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>205204.12</v>
+        <v>205189.4</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9955,11 +10015,183 @@
         <v>-3231.85</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>205239.44</v>
+        <v>205356.13</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>197205.41</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>2741.16</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>-9.52</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>205225.28</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>194464.26</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>2703.05</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>205234.8</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>191761.2</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>2665.48</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>205224.72</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>189095.72</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>2628.43</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>205234.95</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose12_portfolio_daily.xlsx
+++ b/output/quickfixclose12_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>178,757.72</t>
+          <t>177,052.59</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+78.76%</t>
+          <t>+77.05%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>185,091  (+85.09%)</t>
+          <t>183,346  (+83.35%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4,059  (6.3 pts of return)</t>
+          <t>4,078  (6.3 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.7x</t>
+          <t>3.6x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,310  (-1.27%)</t>
+          <t>-1,316  (-1.27%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5847,26 +5847,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>178757.72</v>
+        <v>178863.35</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>11999.65</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>166863.7</v>
+      </c>
+      <c r="E190" t="n">
+        <v>7</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 1,685)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>177052.59</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>178757.72</v>
-      </c>
-      <c r="E190" t="n">
+      <c r="D191" s="5" t="n">
+        <v>177052.59</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 1,685)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 1,669); NY_Palladium_Futures short (risk 1,652)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX stop (-1,697); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9964,7 +9992,7 @@
         <v>-35.32</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>205189.4</v>
+        <v>202530.46</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -10058,7 +10086,7 @@
         <v>-9.52</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>205225.28</v>
+        <v>202566.34</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -10101,7 +10129,7 @@
         <v>-0.15</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>205234.8</v>
+        <v>202592.89</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -10144,7 +10172,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>205224.72</v>
+        <v>202565.78</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -10168,14 +10196,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G85" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I85" s="5" t="n">
         <v>189095.72</v>
@@ -10184,12 +10220,98 @@
         <v>2628.43</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>-4.49</v>
+        <v>-2646.4</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>205234.95</v>
+        <v>202593.04</v>
       </c>
       <c r="M85" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>186467.29</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>2591.9</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>-7.01</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>202585.88</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>183875.4</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>2555.87</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>-10.02</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>202575.86</v>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
